--- a/ecosysem/reactions/Excel/metabolisms.xlsx
+++ b/ecosysem/reactions/Excel/metabolisms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartinez\Documents\GitHub\EcoSysEM\ecosysem\reactions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F30EFC-B9DB-4B89-BD78-2D9464B50BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BBB7D1-40A5-489B-9C54-7CBED64A073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Compounds</t>
   </si>
@@ -108,6 +108,17 @@
   </si>
   <si>
     <t>Gas complete ammonia oxidation (gCMX)</t>
+  </si>
+  <si>
+    <t>Hydrogen-dependent DNRA from NO2-
+(H2-DNO2RA)</t>
+  </si>
+  <si>
+    <t>Hydrogen-dependent DNRA from NO3-
+(H2-DNO3RA)</t>
+  </si>
+  <si>
+    <t>NH4+</t>
   </si>
 </sst>
 </file>
@@ -446,18 +457,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="4" customWidth="1"/>
-    <col min="5" max="9" width="21.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="4" customWidth="1"/>
+    <col min="5" max="9" width="21.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="22" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +498,14 @@
       <c r="I1" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -499,8 +518,14 @@
       <c r="F2" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="4">
+        <v>-2</v>
+      </c>
+      <c r="K2" s="4">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -522,8 +547,14 @@
       <c r="I3" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="4">
+        <v>3</v>
+      </c>
+      <c r="K3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -552,7 +583,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -560,7 +591,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -571,15 +602,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="4">
         <v>-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="4">
+        <v>-4</v>
+      </c>
+      <c r="K7" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -587,7 +624,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -595,65 +632,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="I11" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="E12" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="G15" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="H16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I17" s="4">
         <v>1</v>
       </c>
     </row>
